--- a/data/coastal_datacenter_city_manifest.xlsx
+++ b/data/coastal_datacenter_city_manifest.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coastal_data_center\Code\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625D545C-A710-42E8-B69D-55159FA633CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75E0E17-5EE5-4B78-BAF2-3D7E29FCF2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="41180" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="City_manifest" sheetId="1" r:id="rId1"/>
-    <sheet name="Country_summary" sheetId="2" r:id="rId2"/>
-    <sheet name="Method_notes" sheetId="3" r:id="rId3"/>
-    <sheet name="Repository_mapping" sheetId="4" r:id="rId4"/>
+    <sheet name="Country_manifest" sheetId="5" r:id="rId2"/>
+    <sheet name="Country_summary" sheetId="2" r:id="rId3"/>
+    <sheet name="Method_notes" sheetId="3" r:id="rId4"/>
+    <sheet name="Repository_mapping" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="440">
   <si>
     <t>repo_city_index</t>
   </si>
@@ -706,69 +707,12 @@
     <t>https://marine-api.open-meteo.com/v1/marine?latitude=3.2500&amp;longitude=113.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
   </si>
   <si>
-    <t>046_</t>
-  </si>
-  <si>
     <t>Finland</t>
   </si>
   <si>
-    <t>Helsinki</t>
-  </si>
-  <si>
-    <t>Gulf of Finland coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=60.0000&amp;longitude=24.7500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
     <t>https://www.datacentermap.com/finland/</t>
   </si>
   <si>
-    <t>047_</t>
-  </si>
-  <si>
-    <t>Pori</t>
-  </si>
-  <si>
-    <t>Bothnian Sea coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=61.5000&amp;longitude=21.5000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>048_</t>
-  </si>
-  <si>
-    <t>Oulu</t>
-  </si>
-  <si>
-    <t>Bothnian Bay coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=65.0000&amp;longitude=25.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>049_</t>
-  </si>
-  <si>
-    <t>Kemi</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=65.7500&amp;longitude=24.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>050_</t>
-  </si>
-  <si>
-    <t>Jakobstad</t>
-  </si>
-  <si>
-    <t>Gulf of Bothnia coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=63.7500&amp;longitude=22.5000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
     <t>051_</t>
   </si>
   <si>
@@ -1012,126 +956,18 @@
     <t>https://marine-api.open-meteo.com/v1/marine?latitude=48.5000&amp;longitude=-123.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
   </si>
   <si>
-    <t>071_</t>
-  </si>
-  <si>
     <t>Denmark</t>
   </si>
   <si>
-    <t>Copenhagen</t>
-  </si>
-  <si>
-    <t>Øresund coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=55.7500&amp;longitude=12.7500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
     <t>https://www.datacentermap.com/denmark/</t>
   </si>
   <si>
-    <t>072_</t>
-  </si>
-  <si>
-    <t>Varde</t>
-  </si>
-  <si>
-    <t>North Sea coast/nearshore municipality; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=55.5000&amp;longitude=8.0000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>073_</t>
-  </si>
-  <si>
-    <t>Esbjerg</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=55.5000&amp;longitude=8.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>074_</t>
-  </si>
-  <si>
-    <t>Aarhus Bay coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=56.2500&amp;longitude=10.5000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>075_</t>
-  </si>
-  <si>
-    <t>Saeby</t>
-  </si>
-  <si>
-    <t>Kattegat coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=57.2500&amp;longitude=10.7500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>076_</t>
-  </si>
-  <si>
     <t>Spain</t>
   </si>
   <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Mediterranean coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=41.2500&amp;longitude=2.5000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
     <t>https://www.datacentermap.com/spain/</t>
   </si>
   <si>
-    <t>077_</t>
-  </si>
-  <si>
-    <t>Santander</t>
-  </si>
-  <si>
-    <t>Cantabrian Sea coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=43.5000&amp;longitude=-4.0000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>078_</t>
-  </si>
-  <si>
-    <t>Valencia</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=39.2500&amp;longitude=-0.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>079_</t>
-  </si>
-  <si>
-    <t>Bilbao</t>
-  </si>
-  <si>
-    <t>Bay of Biscay / estuary coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=43.5000&amp;longitude=-3.0000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>080_</t>
-  </si>
-  <si>
-    <t>Malaga</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=36.5000&amp;longitude=-4.5000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
     <t>081_</t>
   </si>
   <si>
@@ -1249,111 +1085,18 @@
     <t>No additional DataCenterMap coastal market #5</t>
   </si>
   <si>
-    <t>091_</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
-    <t>Stockholm</t>
-  </si>
-  <si>
-    <t>Baltic Sea archipelago coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=59.2500&amp;longitude=18.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
     <t>https://www.datacentermap.com/sweden/</t>
   </si>
   <si>
-    <t>092_</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=60.7500&amp;longitude=17.5000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>093_</t>
-  </si>
-  <si>
-    <t>Kattegat/North Sea coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=57.7500&amp;longitude=11.7500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>094_</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=55.5000&amp;longitude=12.7500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>095_</t>
-  </si>
-  <si>
-    <t>Pitea</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=65.2500&amp;longitude=21.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>096_</t>
-  </si>
-  <si>
     <t>Thailand</t>
   </si>
   <si>
-    <t>Bangkok</t>
-  </si>
-  <si>
-    <t>Chao Phraya delta / Gulf of Thailand within 20 km; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=13.5000&amp;longitude=100.5000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
     <t>https://www.datacentermap.com/thailand/</t>
   </si>
   <si>
-    <t>097_</t>
-  </si>
-  <si>
-    <t>Chonburi</t>
-  </si>
-  <si>
-    <t>Gulf of Thailand coast; city/metro retained only if market is within 20 km of sea/coastal water and has coastline/estuary/fjord/bay access</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=13.0000&amp;longitude=100.7500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>098_</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=12.5000&amp;longitude=101.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>099_</t>
-  </si>
-  <si>
-    <t>Pattaya</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=12.7500&amp;longitude=100.7500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
-    <t>100_</t>
-  </si>
-  <si>
-    <t>Ban Chang</t>
-  </si>
-  <si>
-    <t>https://marine-api.open-meteo.com/v1/marine?latitude=12.5000&amp;longitude=101.0000&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
-  </si>
-  <si>
     <t>requested_ranks</t>
   </si>
   <si>
@@ -1582,19 +1325,27 @@
     <t>ERA5 wind capacity calculation uses u100,v100,u10,v10,t2m,sp and netCDF files.</t>
   </si>
   <si>
-    <t>Gothenburg</t>
+    <t>country</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Malmo</t>
+    <t>total_gw_2030_Base</t>
+  </si>
+  <si>
+    <t>total_gw_2030_Lift-Off</t>
+  </si>
+  <si>
+    <t>total_gw_2030_High Efficiency</t>
+  </si>
+  <si>
+    <t>total_gw_2030_Headwinds</t>
+  </si>
+  <si>
+    <t>total_gw_2025</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Gavle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Aarhus</t>
+    <t>coastal_share_of_total_pct</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1605,7 +1356,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1625,6 +1376,18 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1653,7 +1416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1677,6 +1440,13 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1748,7 +1518,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CityManifestTable" displayName="CityManifestTable" ref="A1:V101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CityManifestTable" displayName="CityManifestTable" ref="A1:V76">
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="repo_city_index"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="epw_filename_prefix"/>
@@ -1964,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V101"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5027,22 +4797,22 @@
     </row>
     <row r="47" spans="1:22" ht="56">
       <c r="A47" s="6">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D47" s="2">
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F47" s="4">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>25</v>
@@ -5051,41 +4821,41 @@
         <v>1</v>
       </c>
       <c r="I47" s="5">
-        <v>60.25</v>
+        <v>38.75</v>
       </c>
       <c r="J47" s="5">
-        <v>25</v>
+        <v>-9.25</v>
       </c>
       <c r="K47" s="5">
-        <v>60</v>
+        <v>38.5</v>
       </c>
       <c r="L47" s="5">
-        <v>24.75</v>
+        <v>-9.5</v>
       </c>
       <c r="M47" s="5">
-        <v>59.75</v>
+        <v>38.25</v>
       </c>
       <c r="N47" s="5">
-        <v>24.5</v>
+        <v>-9.75</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="R47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>32</v>
@@ -5093,22 +4863,22 @@
     </row>
     <row r="48" spans="1:22" ht="56">
       <c r="A48" s="6">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D48" s="2">
         <v>2</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F48" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>25</v>
@@ -5117,41 +4887,41 @@
         <v>1</v>
       </c>
       <c r="I48" s="5">
-        <v>61.5</v>
+        <v>41.25</v>
       </c>
       <c r="J48" s="5">
-        <v>21.75</v>
+        <v>-8.75</v>
       </c>
       <c r="K48" s="5">
-        <v>61.5</v>
+        <v>41.25</v>
       </c>
       <c r="L48" s="5">
-        <v>21.5</v>
+        <v>-9</v>
       </c>
       <c r="M48" s="5">
-        <v>61.25</v>
+        <v>41.25</v>
       </c>
       <c r="N48" s="5">
-        <v>21.25</v>
+        <v>-9.25</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="T48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U48" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V48" s="2" t="s">
         <v>32</v>
@@ -5159,22 +4929,22 @@
     </row>
     <row r="49" spans="1:22" ht="56">
       <c r="A49" s="6">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D49" s="2">
         <v>3</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F49" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>25</v>
@@ -5183,41 +4953,41 @@
         <v>1</v>
       </c>
       <c r="I49" s="5">
-        <v>65</v>
+        <v>38.75</v>
       </c>
       <c r="J49" s="5">
-        <v>25.5</v>
+        <v>-9.25</v>
       </c>
       <c r="K49" s="5">
-        <v>65</v>
+        <v>38.75</v>
       </c>
       <c r="L49" s="5">
-        <v>25.25</v>
+        <v>-9.5</v>
       </c>
       <c r="M49" s="5">
-        <v>64.75</v>
+        <v>38.5</v>
       </c>
       <c r="N49" s="5">
-        <v>24.75</v>
+        <v>-9.75</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="T49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V49" s="2" t="s">
         <v>32</v>
@@ -5225,22 +4995,22 @@
     </row>
     <row r="50" spans="1:22" ht="56">
       <c r="A50" s="6">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D50" s="2">
         <v>4</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F50" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>25</v>
@@ -5249,41 +5019,41 @@
         <v>1</v>
       </c>
       <c r="I50" s="5">
-        <v>65.75</v>
+        <v>38.75</v>
       </c>
       <c r="J50" s="5">
-        <v>24.5</v>
+        <v>-9</v>
       </c>
       <c r="K50" s="5">
-        <v>65.75</v>
+        <v>38.5</v>
       </c>
       <c r="L50" s="5">
-        <v>24.25</v>
+        <v>-9.25</v>
       </c>
       <c r="M50" s="5">
-        <v>65.5</v>
+        <v>38.25</v>
       </c>
       <c r="N50" s="5">
-        <v>24</v>
+        <v>-9.5</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="R50" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="T50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V50" s="2" t="s">
         <v>32</v>
@@ -5291,22 +5061,22 @@
     </row>
     <row r="51" spans="1:22" ht="56">
       <c r="A51" s="6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D51" s="2">
         <v>5</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F51" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>25</v>
@@ -5315,41 +5085,41 @@
         <v>1</v>
       </c>
       <c r="I51" s="5">
-        <v>63.75</v>
+        <v>41.25</v>
       </c>
       <c r="J51" s="5">
-        <v>22.75</v>
+        <v>-8.75</v>
       </c>
       <c r="K51" s="5">
-        <v>63.75</v>
+        <v>41.25</v>
       </c>
       <c r="L51" s="5">
-        <v>22.5</v>
+        <v>-9</v>
       </c>
       <c r="M51" s="5">
-        <v>63.5</v>
+        <v>41.25</v>
       </c>
       <c r="N51" s="5">
-        <v>22.25</v>
+        <v>-9.25</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="R51" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="T51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U51" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V51" s="2" t="s">
         <v>32</v>
@@ -5357,22 +5127,22 @@
     </row>
     <row r="52" spans="1:22" ht="56">
       <c r="A52" s="6">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D52" s="2">
         <v>1</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F52" s="4">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>25</v>
@@ -5381,41 +5151,41 @@
         <v>1</v>
       </c>
       <c r="I52" s="5">
-        <v>38.75</v>
+        <v>37.5</v>
       </c>
       <c r="J52" s="5">
-        <v>-9.25</v>
+        <v>126.75</v>
       </c>
       <c r="K52" s="5">
-        <v>38.5</v>
+        <v>37.25</v>
       </c>
       <c r="L52" s="5">
-        <v>-9.5</v>
+        <v>126.25</v>
       </c>
       <c r="M52" s="5">
-        <v>38.25</v>
+        <v>37</v>
       </c>
       <c r="N52" s="5">
-        <v>-9.75</v>
+        <v>125.75</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="R52" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="T52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="V52" s="2" t="s">
         <v>32</v>
@@ -5423,22 +5193,22 @@
     </row>
     <row r="53" spans="1:22" ht="56">
       <c r="A53" s="6">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D53" s="2">
         <v>2</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F53" s="4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>25</v>
@@ -5447,41 +5217,41 @@
         <v>1</v>
       </c>
       <c r="I53" s="5">
-        <v>41.25</v>
+        <v>35.25</v>
       </c>
       <c r="J53" s="5">
-        <v>-8.75</v>
+        <v>129</v>
       </c>
       <c r="K53" s="5">
-        <v>41.25</v>
+        <v>35</v>
       </c>
       <c r="L53" s="5">
-        <v>-9</v>
+        <v>129.25</v>
       </c>
       <c r="M53" s="5">
-        <v>41.25</v>
+        <v>34.75</v>
       </c>
       <c r="N53" s="5">
-        <v>-9.25</v>
+        <v>129.5</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="V53" s="2" t="s">
         <v>32</v>
@@ -5489,22 +5259,22 @@
     </row>
     <row r="54" spans="1:22" ht="56">
       <c r="A54" s="6">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D54" s="2">
         <v>3</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F54" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>25</v>
@@ -5513,41 +5283,41 @@
         <v>1</v>
       </c>
       <c r="I54" s="5">
-        <v>38.75</v>
+        <v>35.5</v>
       </c>
       <c r="J54" s="5">
-        <v>-9.25</v>
+        <v>129.25</v>
       </c>
       <c r="K54" s="5">
-        <v>38.75</v>
+        <v>35.25</v>
       </c>
       <c r="L54" s="5">
-        <v>-9.5</v>
+        <v>129.5</v>
       </c>
       <c r="M54" s="5">
-        <v>38.5</v>
+        <v>35</v>
       </c>
       <c r="N54" s="5">
-        <v>-9.75</v>
+        <v>130</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U54" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="V54" s="2" t="s">
         <v>32</v>
@@ -5555,19 +5325,19 @@
     </row>
     <row r="55" spans="1:22" ht="56">
       <c r="A55" s="6">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D55" s="2">
         <v>4</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F55" s="4">
         <v>1</v>
@@ -5579,41 +5349,41 @@
         <v>1</v>
       </c>
       <c r="I55" s="5">
-        <v>38.75</v>
+        <v>36</v>
       </c>
       <c r="J55" s="5">
-        <v>-9</v>
+        <v>126.75</v>
       </c>
       <c r="K55" s="5">
-        <v>38.5</v>
+        <v>36</v>
       </c>
       <c r="L55" s="5">
-        <v>-9.25</v>
+        <v>126.25</v>
       </c>
       <c r="M55" s="5">
-        <v>38.25</v>
+        <v>36</v>
       </c>
       <c r="N55" s="5">
-        <v>-9.5</v>
+        <v>125.75</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" s="2" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U55" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="V55" s="2" t="s">
         <v>32</v>
@@ -5621,19 +5391,19 @@
     </row>
     <row r="56" spans="1:22" ht="56">
       <c r="A56" s="6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D56" s="2">
         <v>5</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F56" s="4">
         <v>1</v>
@@ -5645,41 +5415,41 @@
         <v>1</v>
       </c>
       <c r="I56" s="5">
-        <v>41.25</v>
+        <v>37.75</v>
       </c>
       <c r="J56" s="5">
-        <v>-8.75</v>
+        <v>128.75</v>
       </c>
       <c r="K56" s="5">
-        <v>41.25</v>
+        <v>37.75</v>
       </c>
       <c r="L56" s="5">
-        <v>-9</v>
+        <v>129.25</v>
       </c>
       <c r="M56" s="5">
-        <v>41.25</v>
+        <v>37.75</v>
       </c>
       <c r="N56" s="5">
-        <v>-9.25</v>
+        <v>129.75</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P56" s="2"/>
       <c r="Q56" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U56" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="V56" s="2" t="s">
         <v>32</v>
@@ -5687,22 +5457,22 @@
     </row>
     <row r="57" spans="1:22" ht="56">
       <c r="A57" s="6">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D57" s="2">
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F57" s="4">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>25</v>
@@ -5711,41 +5481,41 @@
         <v>1</v>
       </c>
       <c r="I57" s="5">
-        <v>37.5</v>
+        <v>52.25</v>
       </c>
       <c r="J57" s="5">
-        <v>126.75</v>
+        <v>4.75</v>
       </c>
       <c r="K57" s="5">
-        <v>37.25</v>
+        <v>52.5</v>
       </c>
       <c r="L57" s="5">
-        <v>126.25</v>
+        <v>4.25</v>
       </c>
       <c r="M57" s="5">
-        <v>37</v>
+        <v>52.75</v>
       </c>
       <c r="N57" s="5">
-        <v>125.75</v>
+        <v>4</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="V57" s="2" t="s">
         <v>32</v>
@@ -5753,22 +5523,22 @@
     </row>
     <row r="58" spans="1:22" ht="56">
       <c r="A58" s="6">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F58" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>25</v>
@@ -5777,41 +5547,41 @@
         <v>1</v>
       </c>
       <c r="I58" s="5">
-        <v>35.25</v>
+        <v>52</v>
       </c>
       <c r="J58" s="5">
-        <v>129</v>
+        <v>4.5</v>
       </c>
       <c r="K58" s="5">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="L58" s="5">
-        <v>129.25</v>
+        <v>3.75</v>
       </c>
       <c r="M58" s="5">
-        <v>34.75</v>
+        <v>52</v>
       </c>
       <c r="N58" s="5">
-        <v>129.5</v>
+        <v>3.5</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R58" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="T58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="V58" s="2" t="s">
         <v>32</v>
@@ -5819,22 +5589,22 @@
     </row>
     <row r="59" spans="1:22" ht="56">
       <c r="A59" s="6">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D59" s="2">
         <v>3</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F59" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>25</v>
@@ -5843,29 +5613,29 @@
         <v>1</v>
       </c>
       <c r="I59" s="5">
-        <v>35.5</v>
+        <v>52</v>
       </c>
       <c r="J59" s="5">
-        <v>129.25</v>
+        <v>4.25</v>
       </c>
       <c r="K59" s="5">
-        <v>35.25</v>
+        <v>52</v>
       </c>
       <c r="L59" s="5">
-        <v>129.5</v>
+        <v>4</v>
       </c>
       <c r="M59" s="5">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="N59" s="5">
-        <v>130</v>
+        <v>3.75</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" s="2" t="s">
-        <v>281</v>
+        <v>171</v>
       </c>
       <c r="R59" s="2" t="s">
         <v>28</v>
@@ -5877,7 +5647,7 @@
         <v>30</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="V59" s="2" t="s">
         <v>32</v>
@@ -5885,13 +5655,13 @@
     </row>
     <row r="60" spans="1:22" ht="56">
       <c r="A60" s="6">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>283</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D60" s="2">
         <v>4</v>
@@ -5900,7 +5670,7 @@
         <v>284</v>
       </c>
       <c r="F60" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>25</v>
@@ -5909,41 +5679,41 @@
         <v>1</v>
       </c>
       <c r="I60" s="5">
-        <v>36</v>
+        <v>51.5</v>
       </c>
       <c r="J60" s="5">
-        <v>126.75</v>
+        <v>3.75</v>
       </c>
       <c r="K60" s="5">
-        <v>36</v>
+        <v>51.5</v>
       </c>
       <c r="L60" s="5">
-        <v>126.25</v>
+        <v>3.5</v>
       </c>
       <c r="M60" s="5">
-        <v>36</v>
+        <v>51.5</v>
       </c>
       <c r="N60" s="5">
-        <v>125.75</v>
+        <v>3.25</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" s="2" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="T60" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="V60" s="2" t="s">
         <v>32</v>
@@ -5951,19 +5721,19 @@
     </row>
     <row r="61" spans="1:22" ht="56">
       <c r="A61" s="6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D61" s="2">
         <v>5</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F61" s="4">
         <v>1</v>
@@ -5975,41 +5745,41 @@
         <v>1</v>
       </c>
       <c r="I61" s="5">
-        <v>37.75</v>
+        <v>51.75</v>
       </c>
       <c r="J61" s="5">
-        <v>128.75</v>
+        <v>4.75</v>
       </c>
       <c r="K61" s="5">
-        <v>37.75</v>
+        <v>51.75</v>
       </c>
       <c r="L61" s="5">
-        <v>129.25</v>
+        <v>4</v>
       </c>
       <c r="M61" s="5">
-        <v>37.75</v>
+        <v>51.75</v>
       </c>
       <c r="N61" s="5">
-        <v>129.75</v>
+        <v>3.75</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="R61" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="V61" s="2" t="s">
         <v>32</v>
@@ -6017,22 +5787,22 @@
     </row>
     <row r="62" spans="1:22" ht="56">
       <c r="A62" s="6">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D62" s="2">
         <v>1</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F62" s="4">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>25</v>
@@ -6041,41 +5811,41 @@
         <v>1</v>
       </c>
       <c r="I62" s="5">
-        <v>52.25</v>
+        <v>49.25</v>
       </c>
       <c r="J62" s="5">
-        <v>4.75</v>
+        <v>-123</v>
       </c>
       <c r="K62" s="5">
-        <v>52.5</v>
+        <v>49.25</v>
       </c>
       <c r="L62" s="5">
-        <v>4.25</v>
+        <v>-123.25</v>
       </c>
       <c r="M62" s="5">
-        <v>52.75</v>
+        <v>49.25</v>
       </c>
       <c r="N62" s="5">
-        <v>4</v>
+        <v>-123.75</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" s="2" t="s">
-        <v>292</v>
+        <v>100</v>
       </c>
       <c r="R62" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="V62" s="2" t="s">
         <v>32</v>
@@ -6083,22 +5853,22 @@
     </row>
     <row r="63" spans="1:22" ht="56">
       <c r="A63" s="6">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D63" s="2">
         <v>2</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F63" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>25</v>
@@ -6107,29 +5877,29 @@
         <v>1</v>
       </c>
       <c r="I63" s="5">
-        <v>52</v>
+        <v>44.75</v>
       </c>
       <c r="J63" s="5">
-        <v>4.5</v>
+        <v>-63.5</v>
       </c>
       <c r="K63" s="5">
-        <v>52</v>
+        <v>44.5</v>
       </c>
       <c r="L63" s="5">
-        <v>3.75</v>
+        <v>-63.25</v>
       </c>
       <c r="M63" s="5">
-        <v>52</v>
+        <v>44.25</v>
       </c>
       <c r="N63" s="5">
-        <v>3.5</v>
+        <v>-63</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" s="2" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="R63" s="2" t="s">
         <v>28</v>
@@ -6141,7 +5911,7 @@
         <v>30</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="V63" s="2" t="s">
         <v>32</v>
@@ -6149,13 +5919,13 @@
     </row>
     <row r="64" spans="1:22" ht="56">
       <c r="A64" s="6">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D64" s="2">
         <v>3</v>
@@ -6173,41 +5943,41 @@
         <v>1</v>
       </c>
       <c r="I64" s="5">
-        <v>52</v>
+        <v>45.25</v>
       </c>
       <c r="J64" s="5">
-        <v>4.25</v>
+        <v>-66</v>
       </c>
       <c r="K64" s="5">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L64" s="5">
-        <v>4</v>
+        <v>-66</v>
       </c>
       <c r="M64" s="5">
-        <v>52</v>
+        <v>44.75</v>
       </c>
       <c r="N64" s="5">
-        <v>3.75</v>
+        <v>-66.25</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" s="2" t="s">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="R64" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T64" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="V64" s="2" t="s">
         <v>32</v>
@@ -6215,19 +5985,19 @@
     </row>
     <row r="65" spans="1:22" ht="56">
       <c r="A65" s="6">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D65" s="2">
         <v>4</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F65" s="4">
         <v>2</v>
@@ -6239,41 +6009,41 @@
         <v>1</v>
       </c>
       <c r="I65" s="5">
-        <v>51.5</v>
+        <v>46.25</v>
       </c>
       <c r="J65" s="5">
-        <v>3.75</v>
+        <v>-63.25</v>
       </c>
       <c r="K65" s="5">
-        <v>51.5</v>
+        <v>46.25</v>
       </c>
       <c r="L65" s="5">
-        <v>3.5</v>
+        <v>-63</v>
       </c>
       <c r="M65" s="5">
-        <v>51.5</v>
+        <v>46.25</v>
       </c>
       <c r="N65" s="5">
-        <v>3.25</v>
+        <v>-62.5</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P65" s="2"/>
       <c r="Q65" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="T65" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="V65" s="2" t="s">
         <v>32</v>
@@ -6281,19 +6051,19 @@
     </row>
     <row r="66" spans="1:22" ht="56">
       <c r="A66" s="6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D66" s="2">
         <v>5</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F66" s="4">
         <v>1</v>
@@ -6305,29 +6075,29 @@
         <v>1</v>
       </c>
       <c r="I66" s="5">
-        <v>51.75</v>
+        <v>48.5</v>
       </c>
       <c r="J66" s="5">
-        <v>4.75</v>
+        <v>-123.5</v>
       </c>
       <c r="K66" s="5">
-        <v>51.75</v>
+        <v>48.5</v>
       </c>
       <c r="L66" s="5">
-        <v>4</v>
+        <v>-123.25</v>
       </c>
       <c r="M66" s="5">
-        <v>51.75</v>
+        <v>48.25</v>
       </c>
       <c r="N66" s="5">
-        <v>3.75</v>
+        <v>-123</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" s="2" t="s">
-        <v>308</v>
+        <v>100</v>
       </c>
       <c r="R66" s="2" t="s">
         <v>28</v>
@@ -6339,30 +6109,30 @@
         <v>30</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="V66" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:22" ht="56">
+    <row r="67" spans="1:22" ht="42">
       <c r="A67" s="6">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D67" s="2">
         <v>1</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F67" s="4">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>25</v>
@@ -6371,41 +6141,41 @@
         <v>1</v>
       </c>
       <c r="I67" s="5">
-        <v>49.25</v>
+        <v>-6.25</v>
       </c>
       <c r="J67" s="5">
-        <v>-123</v>
+        <v>106.75</v>
       </c>
       <c r="K67" s="5">
-        <v>49.25</v>
+        <v>-5.75</v>
       </c>
       <c r="L67" s="5">
-        <v>-123.25</v>
+        <v>106.75</v>
       </c>
       <c r="M67" s="5">
-        <v>49.25</v>
+        <v>-5.5</v>
       </c>
       <c r="N67" s="5">
-        <v>-123.75</v>
+        <v>106.75</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" s="2" t="s">
-        <v>100</v>
+        <v>317</v>
       </c>
       <c r="R67" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="V67" s="2" t="s">
         <v>32</v>
@@ -6413,22 +6183,22 @@
     </row>
     <row r="68" spans="1:22" ht="56">
       <c r="A68" s="6">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="D68" s="2">
         <v>2</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F68" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>25</v>
@@ -6437,64 +6207,64 @@
         <v>1</v>
       </c>
       <c r="I68" s="5">
-        <v>44.75</v>
+        <v>1</v>
       </c>
       <c r="J68" s="5">
-        <v>-63.5</v>
+        <v>104</v>
       </c>
       <c r="K68" s="5">
-        <v>44.5</v>
+        <v>1</v>
       </c>
       <c r="L68" s="5">
-        <v>-63.25</v>
+        <v>104.25</v>
       </c>
       <c r="M68" s="5">
-        <v>44.25</v>
+        <v>1</v>
       </c>
       <c r="N68" s="5">
-        <v>-63</v>
+        <v>104.5</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" s="2" t="s">
-        <v>268</v>
+        <v>322</v>
       </c>
       <c r="R68" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="V68" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:22" ht="56">
+    <row r="69" spans="1:22" ht="42">
       <c r="A69" s="6">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D69" s="2">
         <v>3</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F69" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>25</v>
@@ -6503,64 +6273,64 @@
         <v>1</v>
       </c>
       <c r="I69" s="5">
-        <v>45.25</v>
+        <v>-7.25</v>
       </c>
       <c r="J69" s="5">
-        <v>-66</v>
+        <v>112.75</v>
       </c>
       <c r="K69" s="5">
-        <v>45</v>
+        <v>-7</v>
       </c>
       <c r="L69" s="5">
-        <v>-66</v>
+        <v>112.75</v>
       </c>
       <c r="M69" s="5">
-        <v>44.75</v>
+        <v>-6.75</v>
       </c>
       <c r="N69" s="5">
-        <v>-66.25</v>
+        <v>112.75</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="R69" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="T69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="V69" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:22" ht="56">
+    <row r="70" spans="1:22" ht="42">
       <c r="A70" s="6">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D70" s="2">
         <v>4</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="F70" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>25</v>
@@ -6569,64 +6339,64 @@
         <v>1</v>
       </c>
       <c r="I70" s="5">
-        <v>46.25</v>
+        <v>-8.75</v>
       </c>
       <c r="J70" s="5">
-        <v>-63.25</v>
+        <v>115.25</v>
       </c>
       <c r="K70" s="5">
-        <v>46.25</v>
+        <v>-8.75</v>
       </c>
       <c r="L70" s="5">
-        <v>-63</v>
+        <v>115.5</v>
       </c>
       <c r="M70" s="5">
-        <v>46.25</v>
+        <v>-8.75</v>
       </c>
       <c r="N70" s="5">
-        <v>-62.5</v>
+        <v>116</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="R70" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U70" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="V70" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:22" ht="56">
+    <row r="71" spans="1:22" ht="42">
       <c r="A71" s="6">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D71" s="2">
         <v>5</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F71" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>25</v>
@@ -6635,41 +6405,41 @@
         <v>1</v>
       </c>
       <c r="I71" s="5">
-        <v>48.5</v>
+        <v>-5.25</v>
       </c>
       <c r="J71" s="5">
-        <v>-123.5</v>
+        <v>119.5</v>
       </c>
       <c r="K71" s="5">
-        <v>48.5</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="5">
-        <v>-123.25</v>
+        <v>119.25</v>
       </c>
       <c r="M71" s="5">
-        <v>48.25</v>
+        <v>-4.75</v>
       </c>
       <c r="N71" s="5">
-        <v>-123</v>
+        <v>119.25</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" s="2" t="s">
-        <v>100</v>
+        <v>334</v>
       </c>
       <c r="R71" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="T71" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U71" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="V71" s="2" t="s">
         <v>32</v>
@@ -6677,22 +6447,22 @@
     </row>
     <row r="72" spans="1:22" ht="56">
       <c r="A72" s="6">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D72" s="2">
         <v>1</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F72" s="4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>25</v>
@@ -6701,41 +6471,41 @@
         <v>1</v>
       </c>
       <c r="I72" s="5">
-        <v>55.75</v>
+        <v>1.25</v>
       </c>
       <c r="J72" s="5">
-        <v>12.5</v>
+        <v>103.75</v>
       </c>
       <c r="K72" s="5">
-        <v>55.75</v>
+        <v>1.25</v>
       </c>
       <c r="L72" s="5">
-        <v>12.75</v>
+        <v>104</v>
       </c>
       <c r="M72" s="5">
-        <v>55.75</v>
+        <v>1</v>
       </c>
       <c r="N72" s="5">
-        <v>13</v>
+        <v>104.25</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="R72" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>333</v>
+        <v>210</v>
       </c>
       <c r="T72" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U72" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="V72" s="2" t="s">
         <v>32</v>
@@ -6743,65 +6513,65 @@
     </row>
     <row r="73" spans="1:22" ht="56">
       <c r="A73" s="6">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F73" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="H73" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="5">
-        <v>55.5</v>
+        <v>1.25</v>
       </c>
       <c r="J73" s="5">
-        <v>8.5</v>
+        <v>103.75</v>
       </c>
       <c r="K73" s="5">
-        <v>55.5</v>
+        <v>1.25</v>
       </c>
       <c r="L73" s="5">
-        <v>8</v>
+        <v>103.5</v>
       </c>
       <c r="M73" s="5">
-        <v>55.5</v>
+        <v>1</v>
       </c>
       <c r="N73" s="5">
-        <v>7.75</v>
+        <v>103.5</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="R73" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="T73" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U73" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="V73" s="2" t="s">
         <v>32</v>
@@ -6809,65 +6579,49 @@
     </row>
     <row r="74" spans="1:22" ht="56">
       <c r="A74" s="6">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D74" s="2">
         <v>3</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F74" s="4">
-        <v>10</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="F74" s="4"/>
       <c r="G74" s="2" t="s">
-        <v>25</v>
+        <v>347</v>
       </c>
       <c r="H74" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I74" s="5">
-        <v>55.5</v>
-      </c>
-      <c r="J74" s="5">
-        <v>8.5</v>
-      </c>
-      <c r="K74" s="5">
-        <v>55.5</v>
-      </c>
-      <c r="L74" s="5">
-        <v>8.25</v>
-      </c>
-      <c r="M74" s="5">
-        <v>55.25</v>
-      </c>
-      <c r="N74" s="5">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
       <c r="O74" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" s="2" t="s">
-        <v>171</v>
+        <v>348</v>
       </c>
       <c r="R74" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S74" s="2" t="s">
-        <v>341</v>
-      </c>
+      <c r="S74" s="2"/>
       <c r="T74" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U74" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="V74" s="2" t="s">
         <v>32</v>
@@ -6875,65 +6629,49 @@
     </row>
     <row r="75" spans="1:22" ht="56">
       <c r="A75" s="6">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D75" s="2">
         <v>4</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F75" s="4">
-        <v>5</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="F75" s="4"/>
       <c r="G75" s="2" t="s">
-        <v>25</v>
+        <v>347</v>
       </c>
       <c r="H75" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I75" s="5">
-        <v>56.25</v>
-      </c>
-      <c r="J75" s="5">
-        <v>10.25</v>
-      </c>
-      <c r="K75" s="5">
-        <v>56.25</v>
-      </c>
-      <c r="L75" s="5">
-        <v>10.5</v>
-      </c>
-      <c r="M75" s="5">
-        <v>56.25</v>
-      </c>
-      <c r="N75" s="5">
-        <v>10.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
       <c r="O75" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="R75" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S75" s="2" t="s">
-        <v>344</v>
-      </c>
+      <c r="S75" s="2"/>
       <c r="T75" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="V75" s="2" t="s">
         <v>32</v>
@@ -6941,1675 +6679,57 @@
     </row>
     <row r="76" spans="1:22" ht="56">
       <c r="A76" s="6">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D76" s="2">
         <v>5</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="F76" s="4">
-        <v>3</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="F76" s="4"/>
       <c r="G76" s="2" t="s">
-        <v>25</v>
+        <v>347</v>
       </c>
       <c r="H76" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I76" s="5">
-        <v>57.25</v>
-      </c>
-      <c r="J76" s="5">
-        <v>10.5</v>
-      </c>
-      <c r="K76" s="5">
-        <v>57.25</v>
-      </c>
-      <c r="L76" s="5">
-        <v>10.75</v>
-      </c>
-      <c r="M76" s="5">
-        <v>57.25</v>
-      </c>
-      <c r="N76" s="5">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
       <c r="O76" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R76" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S76" s="2" t="s">
-        <v>348</v>
-      </c>
+      <c r="S76" s="2"/>
       <c r="T76" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U76" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="V76" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:22" ht="56">
-      <c r="A77" s="6">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D77" s="2">
-        <v>1</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F77" s="4">
-        <v>30</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H77" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I77" s="5">
-        <v>41.5</v>
-      </c>
-      <c r="J77" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="K77" s="5">
-        <v>41.25</v>
-      </c>
-      <c r="L77" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="M77" s="5">
-        <v>41</v>
-      </c>
-      <c r="N77" s="5">
-        <v>2.75</v>
-      </c>
-      <c r="O77" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="R77" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="T77" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U77" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="V77" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" ht="56">
-      <c r="A78" s="6">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D78" s="2">
-        <v>2</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F78" s="4">
-        <v>12</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H78" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I78" s="5">
-        <v>43.5</v>
-      </c>
-      <c r="J78" s="5">
-        <v>-3.75</v>
-      </c>
-      <c r="K78" s="5">
-        <v>43.5</v>
-      </c>
-      <c r="L78" s="5">
-        <v>-4</v>
-      </c>
-      <c r="M78" s="5">
-        <v>43.75</v>
-      </c>
-      <c r="N78" s="5">
-        <v>-4.25</v>
-      </c>
-      <c r="O78" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="R78" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S78" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="T78" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U78" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" ht="56">
-      <c r="A79" s="6">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D79" s="2">
-        <v>3</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F79" s="4">
-        <v>11</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H79" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I79" s="5">
-        <v>39.5</v>
-      </c>
-      <c r="J79" s="5">
-        <v>-0.5</v>
-      </c>
-      <c r="K79" s="5">
-        <v>39.25</v>
-      </c>
-      <c r="L79" s="5">
-        <v>-0.25</v>
-      </c>
-      <c r="M79" s="5">
-        <v>39</v>
-      </c>
-      <c r="N79" s="5">
-        <v>0</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="R79" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="T79" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U79" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="V79" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" ht="56">
-      <c r="A80" s="6">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D80" s="2">
-        <v>4</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F80" s="4">
-        <v>9</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H80" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I80" s="5">
-        <v>43.25</v>
-      </c>
-      <c r="J80" s="5">
-        <v>-3</v>
-      </c>
-      <c r="K80" s="5">
-        <v>43.5</v>
-      </c>
-      <c r="L80" s="5">
-        <v>-3</v>
-      </c>
-      <c r="M80" s="5">
-        <v>43.75</v>
-      </c>
-      <c r="N80" s="5">
-        <v>-3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" ht="56">
-      <c r="A81" s="6">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D81" s="2">
-        <v>5</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F81" s="4">
-        <v>7</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H81" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I81" s="5">
-        <v>36.75</v>
-      </c>
-      <c r="J81" s="5">
-        <v>-4.5</v>
-      </c>
-      <c r="K81" s="5">
-        <v>36.5</v>
-      </c>
-      <c r="L81" s="5">
-        <v>-4.5</v>
-      </c>
-      <c r="M81" s="5">
-        <v>36.25</v>
-      </c>
-      <c r="N81" s="5">
-        <v>-4.5</v>
-      </c>
-      <c r="O81" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P81" s="2"/>
-      <c r="Q81" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="R81" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S81" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="T81" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U81" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="V81" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" ht="42">
-      <c r="A82" s="6">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D82" s="2">
-        <v>1</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F82" s="4">
-        <v>103</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H82" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I82" s="5">
-        <v>-6.25</v>
-      </c>
-      <c r="J82" s="5">
-        <v>106.75</v>
-      </c>
-      <c r="K82" s="5">
-        <v>-5.75</v>
-      </c>
-      <c r="L82" s="5">
-        <v>106.75</v>
-      </c>
-      <c r="M82" s="5">
-        <v>-5.5</v>
-      </c>
-      <c r="N82" s="5">
-        <v>106.75</v>
-      </c>
-      <c r="O82" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P82" s="2"/>
-      <c r="Q82" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="R82" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S82" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="T82" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U82" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="V82" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" ht="56">
-      <c r="A83" s="6">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D83" s="2">
-        <v>2</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F83" s="4">
-        <v>15</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H83" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I83" s="5">
-        <v>1</v>
-      </c>
-      <c r="J83" s="5">
-        <v>104</v>
-      </c>
-      <c r="K83" s="5">
-        <v>1</v>
-      </c>
-      <c r="L83" s="5">
-        <v>104.25</v>
-      </c>
-      <c r="M83" s="5">
-        <v>1</v>
-      </c>
-      <c r="N83" s="5">
-        <v>104.5</v>
-      </c>
-      <c r="O83" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P83" s="2"/>
-      <c r="Q83" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="R83" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S83" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="T83" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U83" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" ht="42">
-      <c r="A84" s="6">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D84" s="2">
-        <v>3</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F84" s="4">
-        <v>8</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H84" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I84" s="5">
-        <v>-7.25</v>
-      </c>
-      <c r="J84" s="5">
-        <v>112.75</v>
-      </c>
-      <c r="K84" s="5">
-        <v>-7</v>
-      </c>
-      <c r="L84" s="5">
-        <v>112.75</v>
-      </c>
-      <c r="M84" s="5">
-        <v>-6.75</v>
-      </c>
-      <c r="N84" s="5">
-        <v>112.75</v>
-      </c>
-      <c r="O84" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P84" s="2"/>
-      <c r="Q84" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="R84" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S84" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="T84" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U84" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="V84" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" ht="42">
-      <c r="A85" s="6">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D85" s="2">
-        <v>4</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="F85" s="4">
-        <v>8</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H85" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I85" s="5">
-        <v>-8.75</v>
-      </c>
-      <c r="J85" s="5">
-        <v>115.25</v>
-      </c>
-      <c r="K85" s="5">
-        <v>-8.75</v>
-      </c>
-      <c r="L85" s="5">
-        <v>115.5</v>
-      </c>
-      <c r="M85" s="5">
-        <v>-8.75</v>
-      </c>
-      <c r="N85" s="5">
-        <v>116</v>
-      </c>
-      <c r="O85" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P85" s="2"/>
-      <c r="Q85" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="R85" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S85" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="T85" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U85" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="V85" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" ht="42">
-      <c r="A86" s="6">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D86" s="2">
-        <v>5</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="F86" s="4">
-        <v>3</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H86" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I86" s="5">
-        <v>-5.25</v>
-      </c>
-      <c r="J86" s="5">
-        <v>119.5</v>
-      </c>
-      <c r="K86" s="5">
-        <v>-5</v>
-      </c>
-      <c r="L86" s="5">
-        <v>119.25</v>
-      </c>
-      <c r="M86" s="5">
-        <v>-4.75</v>
-      </c>
-      <c r="N86" s="5">
-        <v>119.25</v>
-      </c>
-      <c r="O86" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P86" s="2"/>
-      <c r="Q86" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="R86" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S86" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="T86" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U86" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="V86" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22" ht="56">
-      <c r="A87" s="6">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D87" s="2">
-        <v>1</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F87" s="4">
-        <v>66</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H87" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I87" s="5">
-        <v>1.25</v>
-      </c>
-      <c r="J87" s="5">
-        <v>103.75</v>
-      </c>
-      <c r="K87" s="5">
-        <v>1.25</v>
-      </c>
-      <c r="L87" s="5">
-        <v>104</v>
-      </c>
-      <c r="M87" s="5">
-        <v>1</v>
-      </c>
-      <c r="N87" s="5">
-        <v>104.25</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="R87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S87" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="T87" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U87" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="V87" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22" ht="56">
-      <c r="A88" s="6">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D88" s="2">
-        <v>2</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F88" s="4">
-        <v>0</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="H88" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I88" s="5">
-        <v>1.25</v>
-      </c>
-      <c r="J88" s="5">
-        <v>103.75</v>
-      </c>
-      <c r="K88" s="5">
-        <v>1.25</v>
-      </c>
-      <c r="L88" s="5">
-        <v>103.5</v>
-      </c>
-      <c r="M88" s="5">
-        <v>1</v>
-      </c>
-      <c r="N88" s="5">
-        <v>103.5</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P88" s="2"/>
-      <c r="Q88" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="R88" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S88" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="T88" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U88" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="V88" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22" ht="56">
-      <c r="A89" s="6">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D89" s="2">
-        <v>3</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="F89" s="4"/>
-      <c r="G89" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="H89" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I89" s="5"/>
-      <c r="J89" s="5"/>
-      <c r="K89" s="5"/>
-      <c r="L89" s="5"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="5"/>
-      <c r="O89" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P89" s="2"/>
-      <c r="Q89" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R89" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S89" s="2"/>
-      <c r="T89" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U89" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="V89" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" ht="56">
-      <c r="A90" s="6">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D90" s="2">
-        <v>4</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F90" s="4"/>
-      <c r="G90" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="H90" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
-      <c r="O90" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R90" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S90" s="2"/>
-      <c r="T90" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U90" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="V90" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" ht="56">
-      <c r="A91" s="6">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D91" s="2">
-        <v>5</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F91" s="4"/>
-      <c r="G91" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="H91" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="5"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P91" s="2"/>
-      <c r="Q91" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R91" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S91" s="2"/>
-      <c r="T91" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U91" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="V91" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22" ht="56">
-      <c r="A92" s="6">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D92" s="2">
-        <v>1</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F92" s="4">
-        <v>48</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H92" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I92" s="5">
-        <v>59.25</v>
-      </c>
-      <c r="J92" s="5">
-        <v>18</v>
-      </c>
-      <c r="K92" s="5">
-        <v>59.25</v>
-      </c>
-      <c r="L92" s="5">
-        <v>18.25</v>
-      </c>
-      <c r="M92" s="5">
-        <v>59.25</v>
-      </c>
-      <c r="N92" s="5">
-        <v>18.75</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P92" s="2"/>
-      <c r="Q92" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="R92" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S92" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="T92" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U92" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="V92" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22" ht="56">
-      <c r="A93" s="6">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D93" s="2">
-        <v>2</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F93" s="4">
-        <v>14</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H93" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I93" s="5">
-        <v>60.75</v>
-      </c>
-      <c r="J93" s="5">
-        <v>17.25</v>
-      </c>
-      <c r="K93" s="5">
-        <v>60.75</v>
-      </c>
-      <c r="L93" s="5">
-        <v>17.5</v>
-      </c>
-      <c r="M93" s="5">
-        <v>60.75</v>
-      </c>
-      <c r="N93" s="5">
-        <v>18</v>
-      </c>
-      <c r="O93" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P93" s="2"/>
-      <c r="Q93" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="R93" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S93" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="T93" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U93" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="V93" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22" ht="56">
-      <c r="A94" s="6">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D94" s="2">
-        <v>3</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F94" s="4">
-        <v>11</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H94" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I94" s="5">
-        <v>57.75</v>
-      </c>
-      <c r="J94" s="5">
-        <v>12</v>
-      </c>
-      <c r="K94" s="5">
-        <v>57.75</v>
-      </c>
-      <c r="L94" s="5">
-        <v>11.75</v>
-      </c>
-      <c r="M94" s="5">
-        <v>57.5</v>
-      </c>
-      <c r="N94" s="5">
-        <v>11.5</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P94" s="2"/>
-      <c r="Q94" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="R94" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S94" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="T94" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U94" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="V94" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" ht="56">
-      <c r="A95" s="6">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D95" s="2">
-        <v>4</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F95" s="4">
-        <v>5</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H95" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I95" s="5">
-        <v>55.5</v>
-      </c>
-      <c r="J95" s="5">
-        <v>13</v>
-      </c>
-      <c r="K95" s="5">
-        <v>55.5</v>
-      </c>
-      <c r="L95" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="M95" s="5">
-        <v>55.25</v>
-      </c>
-      <c r="N95" s="5">
-        <v>12.5</v>
-      </c>
-      <c r="O95" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P95" s="2"/>
-      <c r="Q95" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="R95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S95" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="T95" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U95" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="V95" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="96" spans="1:22" ht="56">
-      <c r="A96" s="6">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D96" s="2">
-        <v>5</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F96" s="4">
-        <v>2</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H96" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I96" s="5">
-        <v>65.25</v>
-      </c>
-      <c r="J96" s="5">
-        <v>21.5</v>
-      </c>
-      <c r="K96" s="5">
-        <v>65</v>
-      </c>
-      <c r="L96" s="5">
-        <v>22</v>
-      </c>
-      <c r="M96" s="5">
-        <v>65</v>
-      </c>
-      <c r="N96" s="5">
-        <v>21</v>
-      </c>
-      <c r="O96" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P96" s="2"/>
-      <c r="Q96" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="R96" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S96" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="T96" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U96" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="V96" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="97" spans="1:22" ht="56">
-      <c r="A97" s="6">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D97" s="2">
-        <v>1</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F97" s="4">
-        <v>46</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H97" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I97" s="5">
-        <v>13.75</v>
-      </c>
-      <c r="J97" s="5">
-        <v>100.5</v>
-      </c>
-      <c r="K97" s="5">
-        <v>13.5</v>
-      </c>
-      <c r="L97" s="5">
-        <v>100.5</v>
-      </c>
-      <c r="M97" s="5">
-        <v>13.25</v>
-      </c>
-      <c r="N97" s="5">
-        <v>100.5</v>
-      </c>
-      <c r="O97" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P97" s="2"/>
-      <c r="Q97" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="R97" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S97" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="T97" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U97" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="V97" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="98" spans="1:22" ht="56">
-      <c r="A98" s="6">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D98" s="2">
-        <v>2</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F98" s="4">
-        <v>5</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H98" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I98" s="5">
-        <v>13.25</v>
-      </c>
-      <c r="J98" s="5">
-        <v>101</v>
-      </c>
-      <c r="K98" s="5">
-        <v>13</v>
-      </c>
-      <c r="L98" s="5">
-        <v>100.75</v>
-      </c>
-      <c r="M98" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="N98" s="5">
-        <v>100.75</v>
-      </c>
-      <c r="O98" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P98" s="2"/>
-      <c r="Q98" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="R98" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S98" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="T98" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U98" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="V98" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="99" spans="1:22" ht="56">
-      <c r="A99" s="6">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D99" s="2">
-        <v>3</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F99" s="4">
-        <v>3</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H99" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I99" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="J99" s="5">
-        <v>101.25</v>
-      </c>
-      <c r="K99" s="5">
-        <v>12.5</v>
-      </c>
-      <c r="L99" s="5">
-        <v>101.25</v>
-      </c>
-      <c r="M99" s="5">
-        <v>12.25</v>
-      </c>
-      <c r="N99" s="5">
-        <v>101.25</v>
-      </c>
-      <c r="O99" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P99" s="2"/>
-      <c r="Q99" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="R99" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U99" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="V99" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="100" spans="1:22" ht="56">
-      <c r="A100" s="6">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D100" s="2">
-        <v>4</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F100" s="4">
-        <v>3</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H100" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I100" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="J100" s="5">
-        <v>101</v>
-      </c>
-      <c r="K100" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="L100" s="5">
-        <v>100.75</v>
-      </c>
-      <c r="M100" s="5">
-        <v>12.5</v>
-      </c>
-      <c r="N100" s="5">
-        <v>100.75</v>
-      </c>
-      <c r="O100" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P100" s="2"/>
-      <c r="Q100" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="R100" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="T100" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U100" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="V100" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="101" spans="1:22" ht="56">
-      <c r="A101" s="6">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D101" s="2">
-        <v>5</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F101" s="4">
-        <v>1</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H101" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I101" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="J101" s="5">
-        <v>101</v>
-      </c>
-      <c r="K101" s="5">
-        <v>12.5</v>
-      </c>
-      <c r="L101" s="5">
-        <v>101</v>
-      </c>
-      <c r="M101" s="5">
-        <v>12.25</v>
-      </c>
-      <c r="N101" s="5">
-        <v>101</v>
-      </c>
-      <c r="O101" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P101" s="2"/>
-      <c r="Q101" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="R101" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S101" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="T101" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U101" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="V101" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G101">
+  <conditionalFormatting sqref="G2:G76">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$G2="valid_selected"</formula>
     </cfRule>
@@ -8620,7 +6740,7 @@
       <formula>$G2="listed_zero_count"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H101">
+  <conditionalFormatting sqref="H2:H76">
     <cfRule type="expression" dxfId="1" priority="4">
       <formula>$H2=TRUE</formula>
     </cfRule>
@@ -8636,6 +6756,388 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26BFE8B7-7726-416D-AD1C-FD8BA2A70B8B}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="16384" width="8.6640625" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="42">
+      <c r="A1" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="8">
+        <v>32.660674546501248</v>
+      </c>
+      <c r="C2" s="8">
+        <v>32.25</v>
+      </c>
+      <c r="D2" s="8">
+        <v>60.359786</v>
+      </c>
+      <c r="E2" s="8">
+        <v>81.426890999999998</v>
+      </c>
+      <c r="F2" s="8">
+        <v>49.426229999999997</v>
+      </c>
+      <c r="G2" s="8">
+        <v>42.226073</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="8">
+        <v>6.7541520000000004</v>
+      </c>
+      <c r="C3" s="8">
+        <v>49.984516999999997</v>
+      </c>
+      <c r="D3" s="8">
+        <v>93.552086000000003</v>
+      </c>
+      <c r="E3" s="8">
+        <v>126.204151</v>
+      </c>
+      <c r="F3" s="8">
+        <v>76.606084999999993</v>
+      </c>
+      <c r="G3" s="8">
+        <v>65.446506999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="8">
+        <v>80.960728000000003</v>
+      </c>
+      <c r="C4" s="8">
+        <v>2.5759479999999999</v>
+      </c>
+      <c r="D4" s="8">
+        <v>4.821199</v>
+      </c>
+      <c r="E4" s="8">
+        <v>6.5039210000000001</v>
+      </c>
+      <c r="F4" s="8">
+        <v>3.9478879999999998</v>
+      </c>
+      <c r="G4" s="8">
+        <v>3.3727809999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="8">
+        <v>55.873430999999997</v>
+      </c>
+      <c r="C5" s="8">
+        <v>2.7571460000000001</v>
+      </c>
+      <c r="D5" s="8">
+        <v>5.1603329999999996</v>
+      </c>
+      <c r="E5" s="8">
+        <v>6.9614209999999996</v>
+      </c>
+      <c r="F5" s="8">
+        <v>4.2255919999999998</v>
+      </c>
+      <c r="G5" s="8">
+        <v>3.6100289999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="8">
+        <v>61.057755999999998</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2.1636609999999998</v>
+      </c>
+      <c r="D6" s="8">
+        <v>4.0495549999999998</v>
+      </c>
+      <c r="E6" s="8">
+        <v>5.4629519999999996</v>
+      </c>
+      <c r="F6" s="8">
+        <v>3.3160189999999998</v>
+      </c>
+      <c r="G6" s="8">
+        <v>2.8329589999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="8">
+        <v>52.523473000000003</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2.2214510000000001</v>
+      </c>
+      <c r="D7" s="8">
+        <v>4.1577159999999997</v>
+      </c>
+      <c r="E7" s="8">
+        <v>5.6088639999999996</v>
+      </c>
+      <c r="F7" s="8">
+        <v>3.4045879999999999</v>
+      </c>
+      <c r="G7" s="8">
+        <v>2.9086249999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="8">
+        <v>93.325040999999999</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.144312</v>
+      </c>
+      <c r="D8" s="8">
+        <v>2.1417190000000002</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.8892340000000001</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1.7537689999999999</v>
+      </c>
+      <c r="G8" s="8">
+        <v>1.498289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" s="8">
+        <v>67.651598000000007</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.393348</v>
+      </c>
+      <c r="D9" s="8">
+        <v>2.6078199999999998</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3.5180150000000001</v>
+      </c>
+      <c r="F9" s="8">
+        <v>2.13544</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1.82436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="8">
+        <v>30.490511000000001</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.3534809999999999</v>
+      </c>
+      <c r="D10" s="8">
+        <v>4.4048239999999996</v>
+      </c>
+      <c r="E10" s="8">
+        <v>5.9422199999999998</v>
+      </c>
+      <c r="F10" s="8">
+        <v>3.606935</v>
+      </c>
+      <c r="G10" s="8">
+        <v>3.081496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="8">
+        <v>93.364525999999998</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.74341000000000002</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.3913819999999999</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.8770089999999999</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1.1393470000000001</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0.97337300000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B12" s="8">
+        <v>40.302742000000002</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1.560465</v>
+      </c>
+      <c r="D12" s="8">
+        <v>2.9205990000000002</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.9399630000000001</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2.3915630000000001</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2.0431720000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="8">
+        <v>60.984205000000003</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1.0049790000000001</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.8809400000000001</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.5374349999999999</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1.540227</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1.3158540000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B14" s="8">
+        <v>76.241333999999995</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.72868200000000005</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1.3638170000000001</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.8398239999999999</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1.116776</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.95408999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="8">
+        <v>99.627255000000005</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.50911499999999998</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.95286999999999999</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.2854460000000001</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.78026700000000004</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.66660200000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="B16" s="8">
+        <v>17.359135999999999</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2.5266869999999999</v>
+      </c>
+      <c r="D16" s="8">
+        <v>4.7290020000000004</v>
+      </c>
+      <c r="E16" s="8">
+        <v>6.3795440000000001</v>
+      </c>
+      <c r="F16" s="8">
+        <v>3.8723920000000001</v>
+      </c>
+      <c r="G16" s="8">
+        <v>3.3082820000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -8654,25 +7156,25 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>443</v>
+        <v>357</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>444</v>
+        <v>358</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>445</v>
+        <v>359</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>446</v>
+        <v>360</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>447</v>
+        <v>361</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>448</v>
+        <v>362</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>449</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8692,13 +7194,13 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>450</v>
+        <v>364</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>451</v>
+        <v>365</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8718,13 +7220,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>453</v>
+        <v>367</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>58</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -8744,13 +7246,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>454</v>
+        <v>368</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -8770,13 +7272,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>455</v>
+        <v>369</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -8796,13 +7298,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>456</v>
+        <v>370</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>124</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -8822,13 +7324,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>457</v>
+        <v>371</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>146</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -8848,13 +7350,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>458</v>
+        <v>372</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>168</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28">
@@ -8874,13 +7376,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>459</v>
+        <v>373</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28">
@@ -8900,18 +7402,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>211</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -8926,18 +7428,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -8952,18 +7454,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -8978,18 +7480,18 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>463</v>
+        <v>377</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -9004,18 +7506,18 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -9030,18 +7532,18 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>465</v>
+        <v>379</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -9056,18 +7558,18 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -9082,18 +7584,18 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>467</v>
+        <v>381</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>370</v>
+        <v>315</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -9108,18 +7610,18 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>468</v>
+        <v>382</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>374</v>
+        <v>319</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28">
       <c r="A19" s="2" t="s">
-        <v>392</v>
+        <v>337</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -9134,18 +7636,18 @@
         <v>4</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>469</v>
+        <v>383</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>394</v>
+        <v>339</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>470</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>409</v>
+        <v>353</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -9160,18 +7662,18 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>471</v>
+        <v>385</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>413</v>
+        <v>354</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>425</v>
+        <v>355</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -9186,13 +7688,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>472</v>
+        <v>386</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>429</v>
+        <v>356</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -9204,7 +7706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -9215,90 +7717,90 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>473</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>474</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>475</v>
+        <v>389</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>476</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28">
       <c r="A3" s="2" t="s">
-        <v>477</v>
+        <v>391</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>478</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28">
       <c r="A4" s="2" t="s">
-        <v>479</v>
+        <v>393</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>480</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28">
       <c r="A5" s="2" t="s">
-        <v>481</v>
+        <v>395</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>482</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28">
       <c r="A6" s="2" t="s">
-        <v>483</v>
+        <v>397</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>484</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28">
       <c r="A7" s="2" t="s">
-        <v>485</v>
+        <v>399</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>486</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28">
       <c r="A8" s="2" t="s">
-        <v>487</v>
+        <v>401</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>488</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="42">
       <c r="A9" s="2" t="s">
-        <v>489</v>
+        <v>403</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>490</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28">
       <c r="A10" s="2" t="s">
-        <v>491</v>
+        <v>405</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>492</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>493</v>
+        <v>407</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>494</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -9310,7 +7812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -9323,86 +7825,86 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>409</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>496</v>
+        <v>410</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>497</v>
+        <v>411</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>498</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28">
       <c r="A2" s="2" t="s">
-        <v>499</v>
+        <v>413</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>501</v>
+        <v>415</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>502</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28">
       <c r="A3" s="2" t="s">
-        <v>503</v>
+        <v>417</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>504</v>
+        <v>418</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>505</v>
+        <v>419</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>506</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>507</v>
+        <v>421</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>509</v>
+        <v>423</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>510</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28">
       <c r="A5" s="2" t="s">
-        <v>511</v>
+        <v>425</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>512</v>
+        <v>426</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>513</v>
+        <v>427</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>514</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28">
       <c r="A6" s="2" t="s">
-        <v>515</v>
+        <v>429</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>516</v>
+        <v>430</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>517</v>
+        <v>431</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>518</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/data/coastal_datacenter_city_manifest.xlsx
+++ b/data/coastal_datacenter_city_manifest.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coastal_data_center\Code\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75E0E17-5EE5-4B78-BAF2-3D7E29FCF2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8E621C-183C-4844-B4B1-FD6338971793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="41180" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="41180" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="City_manifest" sheetId="1" r:id="rId1"/>
     <sheet name="Country_manifest" sheetId="5" r:id="rId2"/>
-    <sheet name="Country_summary" sheetId="2" r:id="rId3"/>
-    <sheet name="Method_notes" sheetId="3" r:id="rId4"/>
-    <sheet name="Repository_mapping" sheetId="4" r:id="rId5"/>
+    <sheet name="Datacenter_scale" sheetId="6" r:id="rId3"/>
+    <sheet name="Country_summary" sheetId="2" r:id="rId4"/>
+    <sheet name="Method_notes" sheetId="3" r:id="rId5"/>
+    <sheet name="Repository_mapping" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="434">
   <si>
     <t>repo_city_index</t>
   </si>
@@ -707,12 +708,6 @@
     <t>https://marine-api.open-meteo.com/v1/marine?latitude=3.2500&amp;longitude=113.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
   </si>
   <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>https://www.datacentermap.com/finland/</t>
-  </si>
-  <si>
     <t>051_</t>
   </si>
   <si>
@@ -956,18 +951,6 @@
     <t>https://marine-api.open-meteo.com/v1/marine?latitude=48.5000&amp;longitude=-123.2500&amp;hourly=sea_surface_temperature&amp;start_date=2025-01-01&amp;end_date=2025-01-02&amp;cell_selection=sea</t>
   </si>
   <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>https://www.datacentermap.com/denmark/</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>https://www.datacentermap.com/spain/</t>
-  </si>
-  <si>
     <t>081_</t>
   </si>
   <si>
@@ -1085,18 +1068,6 @@
     <t>No additional DataCenterMap coastal market #5</t>
   </si>
   <si>
-    <t>Sweden</t>
-  </si>
-  <si>
-    <t>https://www.datacentermap.com/sweden/</t>
-  </si>
-  <si>
-    <t>Thailand</t>
-  </si>
-  <si>
-    <t>https://www.datacentermap.com/thailand/</t>
-  </si>
-  <si>
     <t>requested_ranks</t>
   </si>
   <si>
@@ -1151,9 +1122,6 @@
     <t>Johor Bahru (41); Bayan Baru (2); Kuching (2); George Town (1); Bintulu (1)</t>
   </si>
   <si>
-    <t>Helsinki (47); Pori (14); Oulu (7); Kemi (3); Jakobstad (2)</t>
-  </si>
-  <si>
     <t>Lisbon (24); Porto (11); Carnaxide (2); Barreiro (1); Matosinhos (1)</t>
   </si>
   <si>
@@ -1166,12 +1134,6 @@
     <t>Vancouver (31); Halifax (5); Saint John (4); Charlottetown (2); Victoria (1)</t>
   </si>
   <si>
-    <t>Copenhagen (34); Varde (12); Esbjerg (10); Århus (5); Saeby (3)</t>
-  </si>
-  <si>
-    <t>Barcelona (30); Santander (12); Valencia (11); Bilbao (9); Malaga (7)</t>
-  </si>
-  <si>
     <t>Jakarta (103); Batam (15); Surabaya (8); Denpasar (8); Makassar (3)</t>
   </si>
   <si>
@@ -1179,12 +1141,6 @@
   </si>
   <si>
     <t>Fewer than five nonzero coastal DataCenterMap markets were available; placeholder rows are retained for fixed-rank layout.</t>
-  </si>
-  <si>
-    <t>Stockholm (48); Gävle (14); Gothenburg (11); Malmö (5); Pitea (2)</t>
-  </si>
-  <si>
-    <t>Bangkok (46); Chonburi (5); Rayong (3); Pattaya (3); Ban Chang (1)</t>
   </si>
   <si>
     <t>item</t>
@@ -1347,6 +1303,40 @@
   <si>
     <t>coastal_share_of_total_pct</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>small</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>large</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>count</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>lower bound</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>upper bound</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>median</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1346,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1389,6 +1379,12 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1416,7 +1412,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1441,12 +1437,34 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1548,7 +1566,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CountrySummaryTable" displayName="CountrySummaryTable" ref="A1:H21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CountrySummaryTable" displayName="CountrySummaryTable" ref="A1:H16">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="country"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="requested_ranks"/>
@@ -4800,16 +4818,16 @@
         <v>51</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D47" s="2">
+        <v>1</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D47" s="2">
-        <v>1</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="F47" s="4">
         <v>24</v>
@@ -4843,19 +4861,19 @@
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="R47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>32</v>
@@ -4866,16 +4884,16 @@
         <v>52</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D48" s="2">
         <v>2</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F48" s="4">
         <v>11</v>
@@ -4909,19 +4927,19 @@
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="T48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U48" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="V48" s="2" t="s">
         <v>32</v>
@@ -4932,16 +4950,16 @@
         <v>53</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D49" s="2">
         <v>3</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F49" s="4">
         <v>2</v>
@@ -4975,19 +4993,19 @@
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="T49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="V49" s="2" t="s">
         <v>32</v>
@@ -4998,16 +5016,16 @@
         <v>54</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D50" s="2">
         <v>4</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F50" s="4">
         <v>1</v>
@@ -5041,19 +5059,19 @@
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="R50" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="T50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="V50" s="2" t="s">
         <v>32</v>
@@ -5064,16 +5082,16 @@
         <v>55</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D51" s="2">
         <v>5</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F51" s="4">
         <v>1</v>
@@ -5107,19 +5125,19 @@
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="R51" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="T51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U51" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="V51" s="2" t="s">
         <v>32</v>
@@ -5130,16 +5148,16 @@
         <v>56</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D52" s="2">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="F52" s="4">
         <v>8</v>
@@ -5173,19 +5191,19 @@
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R52" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="T52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="V52" s="2" t="s">
         <v>32</v>
@@ -5196,16 +5214,16 @@
         <v>57</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D53" s="2">
         <v>2</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F53" s="4">
         <v>5</v>
@@ -5239,19 +5257,19 @@
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="T53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="V53" s="2" t="s">
         <v>32</v>
@@ -5262,16 +5280,16 @@
         <v>58</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D54" s="2">
         <v>3</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F54" s="4">
         <v>1</v>
@@ -5305,19 +5323,19 @@
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="T54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U54" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="V54" s="2" t="s">
         <v>32</v>
@@ -5328,16 +5346,16 @@
         <v>59</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D55" s="2">
         <v>4</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F55" s="4">
         <v>1</v>
@@ -5371,19 +5389,19 @@
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="T55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U55" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="V55" s="2" t="s">
         <v>32</v>
@@ -5394,16 +5412,16 @@
         <v>60</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D56" s="2">
         <v>5</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F56" s="4">
         <v>1</v>
@@ -5437,19 +5455,19 @@
       </c>
       <c r="P56" s="2"/>
       <c r="Q56" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U56" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="V56" s="2" t="s">
         <v>32</v>
@@ -5460,16 +5478,16 @@
         <v>61</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D57" s="2">
-        <v>1</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F57" s="4">
         <v>67</v>
@@ -5503,19 +5521,19 @@
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="T57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="V57" s="2" t="s">
         <v>32</v>
@@ -5526,16 +5544,16 @@
         <v>62</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F58" s="4">
         <v>10</v>
@@ -5569,19 +5587,19 @@
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="R58" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="V58" s="2" t="s">
         <v>32</v>
@@ -5592,16 +5610,16 @@
         <v>63</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D59" s="2">
         <v>3</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F59" s="4">
         <v>4</v>
@@ -5641,13 +5659,13 @@
         <v>28</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T59" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="V59" s="2" t="s">
         <v>32</v>
@@ -5658,16 +5676,16 @@
         <v>64</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D60" s="2">
         <v>4</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F60" s="4">
         <v>2</v>
@@ -5701,19 +5719,19 @@
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="T60" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="V60" s="2" t="s">
         <v>32</v>
@@ -5724,16 +5742,16 @@
         <v>65</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D61" s="2">
         <v>5</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F61" s="4">
         <v>1</v>
@@ -5767,19 +5785,19 @@
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R61" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="T61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="V61" s="2" t="s">
         <v>32</v>
@@ -5790,16 +5808,16 @@
         <v>66</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D62" s="2">
+        <v>1</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D62" s="2">
-        <v>1</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="F62" s="4">
         <v>31</v>
@@ -5839,13 +5857,13 @@
         <v>28</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="T62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="V62" s="2" t="s">
         <v>32</v>
@@ -5856,16 +5874,16 @@
         <v>67</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D63" s="2">
         <v>2</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F63" s="4">
         <v>5</v>
@@ -5899,19 +5917,19 @@
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="R63" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="T63" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="V63" s="2" t="s">
         <v>32</v>
@@ -5922,16 +5940,16 @@
         <v>68</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D64" s="2">
         <v>3</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F64" s="4">
         <v>4</v>
@@ -5965,19 +5983,19 @@
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="R64" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="T64" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="V64" s="2" t="s">
         <v>32</v>
@@ -5988,16 +6006,16 @@
         <v>69</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D65" s="2">
         <v>4</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F65" s="4">
         <v>2</v>
@@ -6031,19 +6049,19 @@
       </c>
       <c r="P65" s="2"/>
       <c r="Q65" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="T65" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="V65" s="2" t="s">
         <v>32</v>
@@ -6054,16 +6072,16 @@
         <v>70</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D66" s="2">
         <v>5</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F66" s="4">
         <v>1</v>
@@ -6103,13 +6121,13 @@
         <v>28</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="T66" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="V66" s="2" t="s">
         <v>32</v>
@@ -6120,16 +6138,16 @@
         <v>81</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D67" s="2">
         <v>1</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F67" s="4">
         <v>103</v>
@@ -6163,19 +6181,19 @@
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="R67" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="V67" s="2" t="s">
         <v>32</v>
@@ -6186,16 +6204,16 @@
         <v>82</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D68" s="2">
         <v>2</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F68" s="4">
         <v>15</v>
@@ -6229,19 +6247,19 @@
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="R68" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="V68" s="2" t="s">
         <v>32</v>
@@ -6252,16 +6270,16 @@
         <v>83</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D69" s="2">
         <v>3</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="F69" s="4">
         <v>8</v>
@@ -6295,19 +6313,19 @@
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" s="2" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="R69" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="T69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="V69" s="2" t="s">
         <v>32</v>
@@ -6318,16 +6336,16 @@
         <v>84</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D70" s="2">
         <v>4</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F70" s="4">
         <v>8</v>
@@ -6361,19 +6379,19 @@
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="R70" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U70" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="V70" s="2" t="s">
         <v>32</v>
@@ -6384,16 +6402,16 @@
         <v>85</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D71" s="2">
         <v>5</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F71" s="4">
         <v>3</v>
@@ -6427,19 +6445,19 @@
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="R71" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="T71" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U71" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="V71" s="2" t="s">
         <v>32</v>
@@ -6450,16 +6468,16 @@
         <v>86</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D72" s="2">
         <v>1</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F72" s="4">
         <v>66</v>
@@ -6493,7 +6511,7 @@
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="R72" s="2" t="s">
         <v>28</v>
@@ -6505,7 +6523,7 @@
         <v>30</v>
       </c>
       <c r="U72" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="V72" s="2" t="s">
         <v>32</v>
@@ -6516,22 +6534,22 @@
         <v>87</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F73" s="4">
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="H73" s="3" t="b">
         <v>0</v>
@@ -6559,19 +6577,19 @@
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="R73" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="T73" s="2" t="s">
         <v>30</v>
       </c>
       <c r="U73" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="V73" s="2" t="s">
         <v>32</v>
@@ -6582,20 +6600,20 @@
         <v>88</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D74" s="2">
         <v>3</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="H74" s="3" t="b">
         <v>0</v>
@@ -6611,7 +6629,7 @@
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="R74" s="2" t="s">
         <v>28</v>
@@ -6621,7 +6639,7 @@
         <v>30</v>
       </c>
       <c r="U74" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="V74" s="2" t="s">
         <v>32</v>
@@ -6632,20 +6650,20 @@
         <v>89</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D75" s="2">
         <v>4</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="H75" s="3" t="b">
         <v>0</v>
@@ -6661,7 +6679,7 @@
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="R75" s="2" t="s">
         <v>28</v>
@@ -6671,7 +6689,7 @@
         <v>30</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="V75" s="2" t="s">
         <v>32</v>
@@ -6682,20 +6700,20 @@
         <v>90</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D76" s="2">
         <v>5</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="H76" s="3" t="b">
         <v>0</v>
@@ -6711,7 +6729,7 @@
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="R76" s="2" t="s">
         <v>28</v>
@@ -6721,7 +6739,7 @@
         <v>30</v>
       </c>
       <c r="U76" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="V76" s="2" t="s">
         <v>32</v>
@@ -6759,375 +6777,372 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26BFE8B7-7726-416D-AD1C-FD8BA2A70B8B}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="16384" width="8.6640625" style="7"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="42">
-      <c r="A1" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>437</v>
+      <c r="A1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="8" t="s">
+      <c r="A2" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2">
         <v>32.660674546501248</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2">
         <v>32.25</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2">
         <v>60.359786</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2">
         <v>81.426890999999998</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2">
         <v>49.426229999999997</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2">
         <v>42.226073</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3">
         <v>6.7541520000000004</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>49.984516999999997</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3">
         <v>93.552086000000003</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3">
         <v>126.204151</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3">
         <v>76.606084999999993</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3">
         <v>65.446506999999997</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>80.960728000000003</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>2.5759479999999999</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4">
         <v>4.821199</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4">
         <v>6.5039210000000001</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4">
         <v>3.9478879999999998</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4">
         <v>3.3727809999999998</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <v>55.873430999999997</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>2.7571460000000001</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5">
         <v>5.1603329999999996</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5">
         <v>6.9614209999999996</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5">
         <v>4.2255919999999998</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5">
         <v>3.6100289999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>61.057755999999998</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>2.1636609999999998</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6">
         <v>4.0495549999999998</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6">
         <v>5.4629519999999996</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6">
         <v>3.3160189999999998</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6">
         <v>2.8329589999999998</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>52.523473000000003</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>2.2214510000000001</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7">
         <v>4.1577159999999997</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7">
         <v>5.6088639999999996</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7">
         <v>3.4045879999999999</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7">
         <v>2.9086249999999998</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="8">
+      <c r="A8" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B8">
         <v>93.325040999999999</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>1.144312</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8">
         <v>2.1417190000000002</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8">
         <v>2.8892340000000001</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8">
         <v>1.7537689999999999</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8">
         <v>1.498289</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>67.651598000000007</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>1.393348</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9">
         <v>2.6078199999999998</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9">
         <v>3.5180150000000001</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9">
         <v>2.13544</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9">
         <v>1.82436</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>30.490511000000001</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>2.3534809999999999</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10">
         <v>4.4048239999999996</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10">
         <v>5.9422199999999998</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10">
         <v>3.606935</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10">
         <v>3.081496</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="B11" s="8">
+      <c r="A11" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B11">
         <v>93.364525999999998</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11">
         <v>0.74341000000000002</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11">
         <v>1.3913819999999999</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11">
         <v>1.8770089999999999</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11">
         <v>1.1393470000000001</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11">
         <v>0.97337300000000004</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="B12" s="8">
+      <c r="A12" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12">
         <v>40.302742000000002</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12">
         <v>1.560465</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12">
         <v>2.9205990000000002</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12">
         <v>3.9399630000000001</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12">
         <v>2.3915630000000001</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12">
         <v>2.0431720000000002</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B13" s="8">
+      <c r="A13" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13">
         <v>60.984205000000003</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13">
         <v>1.0049790000000001</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13">
         <v>1.8809400000000001</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13">
         <v>2.5374349999999999</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13">
         <v>1.540227</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13">
         <v>1.3158540000000001</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B14" s="8">
+      <c r="A14" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14">
         <v>76.241333999999995</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14">
         <v>0.72868200000000005</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14">
         <v>1.3638170000000001</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14">
         <v>1.8398239999999999</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14">
         <v>1.116776</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14">
         <v>0.95408999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15">
         <v>99.627255000000005</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15">
         <v>0.50911499999999998</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15">
         <v>0.95286999999999999</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15">
         <v>1.2854460000000001</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15">
         <v>0.78026700000000004</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15">
         <v>0.66660200000000003</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="B16" s="8">
+      <c r="A16" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B16">
         <v>17.359135999999999</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16">
         <v>2.5266869999999999</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16">
         <v>4.7290020000000004</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16">
         <v>6.3795440000000001</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16">
         <v>3.8723920000000001</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16">
         <v>3.3082820000000002</v>
       </c>
     </row>
@@ -7138,8 +7153,102 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29FAB4F-B098-4F19-8041-2F2E40C614AD}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="33">
+      <c r="A1" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.5">
+      <c r="A2" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2" s="12">
+        <v>2016</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.26529999999999998</v>
+      </c>
+      <c r="D2" s="10">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E2" s="10">
+        <v>1.68</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.74299999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="B3" s="12">
+        <v>4586</v>
+      </c>
+      <c r="C3" s="13">
+        <v>0.60340000000000005</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1.708</v>
+      </c>
+      <c r="E3" s="10">
+        <v>18.501999999999999</v>
+      </c>
+      <c r="F3" s="10">
+        <v>4.8970000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="B4" s="10">
+        <v>998</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0.1313</v>
+      </c>
+      <c r="D4" s="10">
+        <v>18.972999999999999</v>
+      </c>
+      <c r="E4" s="10">
+        <v>1095.742</v>
+      </c>
+      <c r="F4" s="10">
+        <v>93.311000000000007</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -7156,25 +7265,25 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7194,13 +7303,13 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -7220,13 +7329,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>58</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -7246,13 +7355,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -7272,13 +7381,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -7298,13 +7407,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>124</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -7324,13 +7433,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>146</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -7350,13 +7459,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>168</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28">
@@ -7376,13 +7485,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28">
@@ -7402,18 +7511,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>211</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -7428,18 +7537,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -7454,18 +7563,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -7480,18 +7589,18 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -7506,18 +7615,18 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -7532,169 +7641,39 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28">
       <c r="A16" s="2" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
       </c>
       <c r="C16" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B17" s="2">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
-        <v>5</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2">
-        <v>5</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="28">
-      <c r="A19" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2">
-        <v>4</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B20" s="2">
-        <v>5</v>
-      </c>
-      <c r="C20" s="2">
-        <v>5</v>
-      </c>
-      <c r="D20" s="2">
-        <v>5</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B21" s="2">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2">
-        <v>5</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -7706,7 +7685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -7717,90 +7696,90 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28">
       <c r="A3" s="2" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28">
       <c r="A4" s="2" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28">
       <c r="A5" s="2" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28">
       <c r="A6" s="2" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28">
       <c r="A7" s="2" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28">
       <c r="A8" s="2" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="42">
       <c r="A9" s="2" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28">
       <c r="A10" s="2" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -7812,7 +7791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -7825,86 +7804,86 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28">
       <c r="A2" s="2" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28">
       <c r="A3" s="2" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28">
       <c r="A5" s="2" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28">
       <c r="A6" s="2" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/data/coastal_datacenter_city_manifest.xlsx
+++ b/data/coastal_datacenter_city_manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coastal_data_center\Code\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8E621C-183C-4844-B4B1-FD6338971793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C434E35-A2ED-46C7-A73F-64F832BD55C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="41180" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1285,18 +1285,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>total_gw_2030_Base</t>
-  </si>
-  <si>
-    <t>total_gw_2030_Lift-Off</t>
-  </si>
-  <si>
-    <t>total_gw_2030_High Efficiency</t>
-  </si>
-  <si>
-    <t>total_gw_2030_Headwinds</t>
-  </si>
-  <si>
     <t>total_gw_2025</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1328,25 +1316,44 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>lower bound</t>
+    <t>median</t>
+  </si>
+  <si>
+    <t>upper_bound</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>upper bound</t>
+    <t>lower_bound</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>median</t>
+    <t>total_gw_2030_Base</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>total_gw_2030_Lift-Off</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>total_gw_2030_High Efficiency</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>total_gw_2030_Headwinds</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="000"/>
+    <numFmt numFmtId="182" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="183" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="186" formatCode="0.0000_);[Red]\(0.0000\)"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1368,22 +1375,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Carlito"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1412,7 +1406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1438,33 +1432,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6778,27 +6760,27 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="42">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>418</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>422</v>
+      <c r="D1" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -6825,7 +6807,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B3">
@@ -6848,7 +6830,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>120</v>
       </c>
       <c r="B4">
@@ -6871,7 +6853,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>98</v>
       </c>
       <c r="B5">
@@ -6894,7 +6876,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>164</v>
       </c>
       <c r="B6">
@@ -6917,7 +6899,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>186</v>
       </c>
       <c r="B7">
@@ -6940,7 +6922,7 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>228</v>
       </c>
       <c r="B8">
@@ -6963,7 +6945,7 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>207</v>
       </c>
       <c r="B9">
@@ -6986,7 +6968,7 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>76</v>
       </c>
       <c r="B10">
@@ -7009,7 +6991,7 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>331</v>
       </c>
       <c r="B11">
@@ -7032,7 +7014,7 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>309</v>
       </c>
       <c r="B12">
@@ -7055,7 +7037,7 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>249</v>
       </c>
       <c r="B13">
@@ -7078,7 +7060,7 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>269</v>
       </c>
       <c r="B14">
@@ -7101,7 +7083,7 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>142</v>
       </c>
       <c r="B15">
@@ -7124,7 +7106,7 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>290</v>
       </c>
       <c r="B16">
@@ -7154,91 +7136,98 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29FAB4F-B098-4F19-8041-2F2E40C614AD}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="16.5">
-      <c r="A2" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="12">
+      <c r="E1" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2" s="10">
         <v>2016</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>0.26529999999999998</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="12">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <v>1.68</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="12">
         <v>0.74299999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="11" t="s">
-        <v>427</v>
-      </c>
-      <c r="B3" s="12">
+      <c r="A3" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" s="10">
         <v>4586</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="11">
         <v>0.60340000000000005</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="12">
         <v>1.708</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="12">
         <v>18.501999999999999</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="12">
         <v>4.8970000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="11" t="s">
-        <v>428</v>
+      <c r="A4" s="13" t="s">
+        <v>424</v>
       </c>
       <c r="B4" s="10">
         <v>998</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="11">
         <v>0.1313</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="12">
         <v>18.972999999999999</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="12">
         <v>1095.742</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="12">
         <v>93.311000000000007</v>
       </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="13"/>
+      <c r="C5" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/coastal_datacenter_city_manifest.xlsx
+++ b/data/coastal_datacenter_city_manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coastal_data_center\Code\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C434E35-A2ED-46C7-A73F-64F832BD55C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121E7122-EEDF-4D6F-80B1-05C32DABB1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="41180" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1316,17 +1316,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>median</t>
-  </si>
-  <si>
-    <t>upper_bound</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>lower_bound</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>total_gw_2030_Base</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1340,6 +1329,18 @@
   </si>
   <si>
     <t>total_gw_2030_Headwinds</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>median_mw</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>upper_bound_mw</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>lower_bound_mw</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1349,9 +1350,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="000"/>
-    <numFmt numFmtId="182" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="183" formatCode="0.0_);[Red]\(0.0\)"/>
-    <numFmt numFmtId="186" formatCode="0.0000_);[Red]\(0.0000\)"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="179" formatCode="0.0000_);[Red]\(0.0000\)"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -1406,7 +1407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1432,21 +1433,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6771,16 +6775,16 @@
         <v>419</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>430</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7155,14 +7159,14 @@
       <c r="C1" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>427</v>
+      <c r="D1" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:6">
